--- a/document/テーブル一覧_20241101.xlsx
+++ b/document/テーブル一覧_20241101.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2\Workspace\Busiframe\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\officinaWork03\busiframe\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69C20FF2-B2CE-41B3-AF8C-89C55AB6443D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317C64E9-6CEB-4FA9-9A13-A3BA5DD34CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0C2D33D0-14BE-4ED7-B421-CFDCED5886B7}"/>
+    <workbookView xWindow="2985" yWindow="2145" windowWidth="18210" windowHeight="11505" xr2:uid="{0C2D33D0-14BE-4ED7-B421-CFDCED5886B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -781,15 +781,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5454D801-327C-4FCC-B2F1-B94D866AB216}">
   <dimension ref="B2:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="str">
         <f>TEXT(B3+1,"00")</f>
         <v>02</v>
@@ -850,7 +850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="str">
         <f t="shared" ref="B5:B17" si="0">TEXT(B4+1,"00")</f>
         <v>03</v>
@@ -871,7 +871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>04</v>
@@ -892,7 +892,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>05</v>
@@ -913,7 +913,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>06</v>
@@ -934,7 +934,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>07</v>
@@ -955,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>08</v>
@@ -976,7 +976,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>09</v>
@@ -997,7 +997,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1018,31 +1018,31 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>15</v>
